--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -2988,7 +2988,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118431131</v>
+        <v>118431303</v>
       </c>
       <c r="B22" t="n">
         <v>97824</v>
@@ -3028,13 +3028,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698215</v>
+        <v>698222</v>
       </c>
       <c r="R22" t="n">
-        <v>6364473</v>
+        <v>6364475</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118431672</v>
+        <v>118431131</v>
       </c>
       <c r="B23" t="n">
-        <v>97821</v>
+        <v>97824</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,13 +3130,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698489</v>
+        <v>698215</v>
       </c>
       <c r="R23" t="n">
-        <v>6364713</v>
+        <v>6364473</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118431651</v>
+        <v>118431155</v>
       </c>
       <c r="B24" t="n">
-        <v>97824</v>
+        <v>97821</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698491</v>
+        <v>698220</v>
       </c>
       <c r="R24" t="n">
-        <v>6364715</v>
+        <v>6364478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118431155</v>
+        <v>118431672</v>
       </c>
       <c r="B25" t="n">
         <v>97821</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698220</v>
+        <v>698489</v>
       </c>
       <c r="R25" t="n">
-        <v>6364478</v>
+        <v>6364713</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118431303</v>
+        <v>118430686</v>
       </c>
       <c r="B26" t="n">
-        <v>97824</v>
+        <v>106120</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3408,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698222</v>
+        <v>698647</v>
       </c>
       <c r="R26" t="n">
-        <v>6364475</v>
+        <v>6364769</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118431413</v>
+        <v>118431651</v>
       </c>
       <c r="B27" t="n">
         <v>97824</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698256</v>
+        <v>698491</v>
       </c>
       <c r="R27" t="n">
-        <v>6364504</v>
+        <v>6364715</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118430686</v>
+        <v>118431413</v>
       </c>
       <c r="B28" t="n">
-        <v>106120</v>
+        <v>97824</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,25 +3612,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3640,13 +3640,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698647</v>
+        <v>698256</v>
       </c>
       <c r="R28" t="n">
-        <v>6364769</v>
+        <v>6364504</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -2886,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118430661</v>
+        <v>118431303</v>
       </c>
       <c r="B21" t="n">
-        <v>42786</v>
+        <v>97824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,25 +2898,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698662</v>
+        <v>698222</v>
       </c>
       <c r="R21" t="n">
-        <v>6364787</v>
+        <v>6364475</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118431303</v>
+        <v>118431155</v>
       </c>
       <c r="B22" t="n">
-        <v>97824</v>
+        <v>97821</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698222</v>
+        <v>698220</v>
       </c>
       <c r="R22" t="n">
-        <v>6364475</v>
+        <v>6364478</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118431131</v>
+        <v>118430661</v>
       </c>
       <c r="B23" t="n">
-        <v>97824</v>
+        <v>42786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,25 +3102,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,13 +3130,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698215</v>
+        <v>698662</v>
       </c>
       <c r="R23" t="n">
-        <v>6364473</v>
+        <v>6364787</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118431155</v>
+        <v>118431131</v>
       </c>
       <c r="B24" t="n">
-        <v>97821</v>
+        <v>97824</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,21 +3208,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698220</v>
+        <v>698215</v>
       </c>
       <c r="R24" t="n">
-        <v>6364478</v>
+        <v>6364473</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118431672</v>
+        <v>118430686</v>
       </c>
       <c r="B25" t="n">
-        <v>97821</v>
+        <v>106120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698489</v>
+        <v>698647</v>
       </c>
       <c r="R25" t="n">
-        <v>6364713</v>
+        <v>6364769</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118430686</v>
+        <v>118431672</v>
       </c>
       <c r="B26" t="n">
-        <v>106120</v>
+        <v>97821</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3408,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698647</v>
+        <v>698489</v>
       </c>
       <c r="R26" t="n">
-        <v>6364769</v>
+        <v>6364713</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118431651</v>
+        <v>118431413</v>
       </c>
       <c r="B27" t="n">
         <v>97824</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698491</v>
+        <v>698256</v>
       </c>
       <c r="R27" t="n">
-        <v>6364715</v>
+        <v>6364504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3600,7 +3600,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118431413</v>
+        <v>118431651</v>
       </c>
       <c r="B28" t="n">
         <v>97824</v>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698256</v>
+        <v>698491</v>
       </c>
       <c r="R28" t="n">
-        <v>6364504</v>
+        <v>6364715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -2889,7 +2889,7 @@
         <v>118431303</v>
       </c>
       <c r="B21" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118431155</v>
+        <v>118431413</v>
       </c>
       <c r="B22" t="n">
-        <v>97821</v>
+        <v>97831</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698220</v>
+        <v>698256</v>
       </c>
       <c r="R22" t="n">
-        <v>6364478</v>
+        <v>6364504</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118430661</v>
+        <v>118431651</v>
       </c>
       <c r="B23" t="n">
-        <v>42786</v>
+        <v>97831</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,25 +3102,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>698662</v>
+        <v>698491</v>
       </c>
       <c r="R23" t="n">
-        <v>6364787</v>
+        <v>6364715</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118431131</v>
+        <v>118430661</v>
       </c>
       <c r="B24" t="n">
-        <v>97824</v>
+        <v>42786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219798</v>
+        <v>101260</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698215</v>
+        <v>698662</v>
       </c>
       <c r="R24" t="n">
-        <v>6364473</v>
+        <v>6364787</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118430686</v>
+        <v>118431672</v>
       </c>
       <c r="B25" t="n">
-        <v>106120</v>
+        <v>97828</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>219797</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698647</v>
+        <v>698489</v>
       </c>
       <c r="R25" t="n">
-        <v>6364769</v>
+        <v>6364713</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118431672</v>
+        <v>118430686</v>
       </c>
       <c r="B26" t="n">
-        <v>97821</v>
+        <v>106127</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3408,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698489</v>
+        <v>698647</v>
       </c>
       <c r="R26" t="n">
-        <v>6364713</v>
+        <v>6364769</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118431413</v>
+        <v>118431131</v>
       </c>
       <c r="B27" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698256</v>
+        <v>698215</v>
       </c>
       <c r="R27" t="n">
-        <v>6364504</v>
+        <v>6364473</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118431651</v>
+        <v>118431155</v>
       </c>
       <c r="B28" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698491</v>
+        <v>698220</v>
       </c>
       <c r="R28" t="n">
-        <v>6364715</v>
+        <v>6364478</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118430661</v>
+        <v>118431672</v>
       </c>
       <c r="B24" t="n">
-        <v>42786</v>
+        <v>97828</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101260</v>
+        <v>219797</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698662</v>
+        <v>698489</v>
       </c>
       <c r="R24" t="n">
-        <v>6364787</v>
+        <v>6364713</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118431672</v>
+        <v>118430661</v>
       </c>
       <c r="B25" t="n">
-        <v>97828</v>
+        <v>42786</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219797</v>
+        <v>101260</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698489</v>
+        <v>698662</v>
       </c>
       <c r="R25" t="n">
-        <v>6364713</v>
+        <v>6364787</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 53103-2021 artfynd.xlsx
+++ b/artfynd/A 53103-2021 artfynd.xlsx
@@ -2886,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118431303</v>
+        <v>118431155</v>
       </c>
       <c r="B21" t="n">
-        <v>97831</v>
+        <v>97828</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,21 +2902,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698222</v>
+        <v>698220</v>
       </c>
       <c r="R21" t="n">
-        <v>6364475</v>
+        <v>6364478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2988,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118431413</v>
+        <v>118431672</v>
       </c>
       <c r="B22" t="n">
-        <v>97831</v>
+        <v>97828</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,21 +3004,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>219797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698256</v>
+        <v>698489</v>
       </c>
       <c r="R22" t="n">
-        <v>6364504</v>
+        <v>6364713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118431672</v>
+        <v>118430686</v>
       </c>
       <c r="B24" t="n">
-        <v>97828</v>
+        <v>106127</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,25 +3204,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219797</v>
+        <v>221849</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>698489</v>
+        <v>698647</v>
       </c>
       <c r="R24" t="n">
-        <v>6364713</v>
+        <v>6364769</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118430661</v>
+        <v>118431131</v>
       </c>
       <c r="B25" t="n">
-        <v>42786</v>
+        <v>97831</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,25 +3306,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101260</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartfläckig blåvinge</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phengaris arion</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>698662</v>
+        <v>698215</v>
       </c>
       <c r="R25" t="n">
-        <v>6364787</v>
+        <v>6364473</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118430686</v>
+        <v>118430661</v>
       </c>
       <c r="B26" t="n">
-        <v>106127</v>
+        <v>42786</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>101260</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>698647</v>
+        <v>698662</v>
       </c>
       <c r="R26" t="n">
-        <v>6364769</v>
+        <v>6364787</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118431131</v>
+        <v>118431303</v>
       </c>
       <c r="B27" t="n">
         <v>97831</v>
@@ -3538,13 +3538,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>698215</v>
+        <v>698222</v>
       </c>
       <c r="R27" t="n">
-        <v>6364473</v>
+        <v>6364475</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118431155</v>
+        <v>118431413</v>
       </c>
       <c r="B28" t="n">
-        <v>97828</v>
+        <v>97831</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219797</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>698220</v>
+        <v>698256</v>
       </c>
       <c r="R28" t="n">
-        <v>6364478</v>
+        <v>6364504</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
